--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
@@ -275,6 +275,9 @@
     <t>Validation messages are accessible to assistive technology.</t>
   </si>
   <si>
+    <t>Low</t>
+  </si>
+  <si>
     <t>Non-functional</t>
   </si>
   <si>
@@ -303,9 +306,6 @@
   </si>
   <si>
     <t>Templates support required locale and accessibility standards.</t>
-  </si>
-  <si>
-    <t>Low</t>
   </si>
   <si>
     <t>AQPI-24, REQ-082, BR-082</t>
@@ -522,7 +522,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T16:16:08.110Z</t>
+    <t>2026-10-11T16:44:58.741Z</t>
   </si>
   <si>
     <t>Column order</t>
@@ -1362,19 +1362,19 @@
         <v>79</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>27</v>
@@ -1388,7 +1388,7 @@
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>45</v>
@@ -1418,7 +1418,7 @@
         <v>24</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>26</v>
@@ -1435,13 +1435,13 @@
     </row>
     <row r="11" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>76</v>
@@ -1453,22 +1453,22 @@
         <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>27</v>
@@ -1503,19 +1503,19 @@
         <v>95</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>96</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>27</v>
@@ -1550,19 +1550,19 @@
         <v>100</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>101</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>27</v>
@@ -1597,19 +1597,19 @@
         <v>105</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>106</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>27</v>
@@ -1907,7 +1907,7 @@
         <v>142</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>143</v>
@@ -1936,7 +1936,7 @@
         <v>144</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>145</v>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
@@ -522,7 +522,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T16:44:58.741Z</t>
+    <t>2026-10-11T17:07:28.044Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
@@ -522,7 +522,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T17:07:28.044Z</t>
+    <t>2026-10-12T01:35:49.601Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="216">
   <si>
     <t>Key</t>
   </si>
@@ -356,6 +356,125 @@
     <t>AQPI-31, REQ-108, BR-108</t>
   </si>
   <si>
+    <t>TC-F-009</t>
+  </si>
+  <si>
+    <t>Guest books a flexible room, then cancels it free of charge more than 48 hours before check-in</t>
+  </si>
+  <si>
+    <t>Verify the release 2.0 cancellation journey across search, cart, reservation and payment: the booking ends cancelled and the payment hold is voided.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search NYC
+2. Book a FLEX rate 30 days ahead
+3. Cancel the reservation
+4. View the reservation</t>
+  </si>
+  <si>
+    <t>selection.ratePlanCode=FLEX; every other booking attribute from the hotel data dictionary examples</t>
+  </si>
+  <si>
+    <t>Booking HTTP 201 CONFIRMED; cancel HTTP 200 CANCELLED with payment VOIDED; the reservation stays CANCELLED</t>
+  </si>
+  <si>
+    <t>functional, eqe, automation</t>
+  </si>
+  <si>
+    <t>AQPI-36, REQ-121, BR-121</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>TC-F-010</t>
+  </si>
+  <si>
+    <t>Guest books, cancels and receives exactly one confirmation and one cancellation e-mail</t>
+  </si>
+  <si>
+    <t>Verify the release 2.0 cancellation journey across reservation and notification: the guest is told once about the booking and once about the cancellation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a FLEX rate
+2. Open the confirmation e-mail
+3. Cancel the reservation
+4. List its messages as support</t>
+  </si>
+  <si>
+    <t>Booking CONFIRMED with its e-mail; cancel HTTP 200 CANCELLED; exactly one CONFIRMATION and one CANCELLATION message</t>
+  </si>
+  <si>
+    <t>AQPI-37, REQ-126, BR-126</t>
+  </si>
+  <si>
+    <t>TC-F-011</t>
+  </si>
+  <si>
+    <t>Guest sorts the results by lowest price, then books a room from the sorted results</t>
+  </si>
+  <si>
+    <t>Verify the sort-and-book journey across the search, cart and reservation services.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search NYC
+2. Sort the results by lowest price
+3. Create a cart for a hotel in the results
+4. Submit the reservation</t>
+  </si>
+  <si>
+    <t>Bookable results in non-decreasing price order; the chosen hotel is in them; HTTP 201 CONFIRMED</t>
+  </si>
+  <si>
+    <t>AQPI-8, REQ-130, BR-130</t>
+  </si>
+  <si>
+    <t>TC-F-012</t>
+  </si>
+  <si>
+    <t>Guest is shown extras, declines them all and books the room only</t>
+  </si>
+  <si>
+    <t>Verify the offers never block the journey: search, offers, cart without extras, reservation and confirmation e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search NYC
+2. Get recommended extras
+3. Create a cart without any extra
+4. Submit the reservation
+5. Open the confirmation e-mail</t>
+  </si>
+  <si>
+    <t>Extras offered; HTTP 201 CONFIRMED with optional extras 0; confirmation e-mail carries the confirmation number</t>
+  </si>
+  <si>
+    <t>AQPI-13, REQ-134, BR-134</t>
+  </si>
+  <si>
+    <t>TC-F-013</t>
+  </si>
+  <si>
+    <t>Guest books a room with breakfast and sees the full booking outcome, matching the confirmation e-mail</t>
+  </si>
+  <si>
+    <t>Verify the guest sees a clear success outcome at the end of the journey, consistent with the e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search NYC
+2. Create a cart with breakfast
+3. Submit the reservation
+4. Read the booking outcome
+5. Open the confirmation e-mail</t>
+  </si>
+  <si>
+    <t>extras.code=BREAKFAST; extras.quantity=1; every other booking attribute from the hotel data dictionary examples</t>
+  </si>
+  <si>
+    <t>Outcome shows confirmation number, hotel, stay dates, breakfast and total; the e-mail has the same confirmation number</t>
+  </si>
+  <si>
+    <t>AQPI-22, REQ-136, BR-136</t>
+  </si>
+  <si>
     <t>Data Set</t>
   </si>
   <si>
@@ -498,6 +617,46 @@
     <t>REQ-108</t>
   </si>
   <si>
+    <t>TD-F-009</t>
+  </si>
+  <si>
+    <t>REQ-121</t>
+  </si>
+  <si>
+    <t>selection.ratePlanCode = FLEX</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>TD-F-010</t>
+  </si>
+  <si>
+    <t>REQ-126</t>
+  </si>
+  <si>
+    <t>TD-F-011</t>
+  </si>
+  <si>
+    <t>REQ-130</t>
+  </si>
+  <si>
+    <t>TD-F-012</t>
+  </si>
+  <si>
+    <t>REQ-134</t>
+  </si>
+  <si>
+    <t>TD-F-013</t>
+  </si>
+  <si>
+    <t>REQ-136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extras.code = BREAKFAST
+extras.quantity = 1</t>
+  </si>
+  <si>
     <t>Field</t>
   </si>
   <si>
@@ -522,7 +681,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-12T01:35:49.601Z</t>
+    <t>2026-10-12T02:10:49.049Z</t>
   </si>
   <si>
     <t>Column order</t>
@@ -566,7 +725,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -583,6 +742,11 @@
         <fgColor rgb="FFF1F3F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF3E4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -596,13 +760,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -944,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1621,6 +1788,241 @@
         <v>29</v>
       </c>
     </row>
+    <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1630,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
@@ -1643,57 +2045,57 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I2" s="2">
         <v>1</v>
@@ -1701,28 +2103,28 @@
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I3" s="2">
         <v>1</v>
@@ -1730,28 +2132,28 @@
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -1759,28 +2161,28 @@
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1788,28 +2190,28 @@
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1817,28 +2219,28 @@
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -1846,28 +2248,28 @@
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
@@ -1875,28 +2277,28 @@
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
@@ -1904,28 +2306,28 @@
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
@@ -1933,28 +2335,28 @@
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
@@ -1962,28 +2364,28 @@
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
@@ -1991,28 +2393,28 @@
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
@@ -2020,30 +2422,175 @@
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="I14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2064,18 +2611,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2083,55 +2630,55 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="B7" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="B8" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
@@ -681,7 +681,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-12T02:10:49.049Z</t>
+    <t>2026-10-12T02:22:46.973Z</t>
   </si>
   <si>
     <t>Column order</t>
